--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12175,6 +12175,1494 @@
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>114715063</v>
+      </c>
+      <c r="B98" t="n">
+        <v>5161</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>577478</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6706556</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>114715047</v>
+      </c>
+      <c r="B99" t="n">
+        <v>90233</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>577488</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6706545</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>114715048</v>
+      </c>
+      <c r="B100" t="n">
+        <v>90233</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>577648</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6706596</v>
+      </c>
+      <c r="S100" t="n">
+        <v>15</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>114715062</v>
+      </c>
+      <c r="B101" t="n">
+        <v>5161</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>577442</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6706535</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>114715046</v>
+      </c>
+      <c r="B102" t="n">
+        <v>90233</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>577701</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6706738</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>114715045</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79038</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>577639</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6706612</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>114715061</v>
+      </c>
+      <c r="B104" t="n">
+        <v>5161</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>577632</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6706672</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>114715040</v>
+      </c>
+      <c r="B105" t="n">
+        <v>5181</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>577824</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6706715</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>114715058</v>
+      </c>
+      <c r="B106" t="n">
+        <v>78096</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>353</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>577639</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6706601</v>
+      </c>
+      <c r="S106" t="n">
+        <v>15</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>114715042</v>
+      </c>
+      <c r="B107" t="n">
+        <v>90197</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>577614</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6706604</v>
+      </c>
+      <c r="S107" t="n">
+        <v>15</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>114715064</v>
+      </c>
+      <c r="B108" t="n">
+        <v>5161</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>577564</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6706581</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>114715060</v>
+      </c>
+      <c r="B109" t="n">
+        <v>5161</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>577818</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6706712</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>114715044</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79038</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>577545</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6706576</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>114715059</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79532</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>577577</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6706592</v>
+      </c>
+      <c r="S111" t="n">
+        <v>15</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, fanny westling</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96918420</v>
+        <v>96919572</v>
       </c>
       <c r="B28" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577882.8871236196</v>
+        <v>577795.2553249649</v>
       </c>
       <c r="R28" t="n">
-        <v>6706866.999139708</v>
+        <v>6706763.066953021</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3982,10 +3982,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96919572</v>
+        <v>96918182</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3994,35 +3994,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577795.2553249649</v>
+        <v>577854.1496546528</v>
       </c>
       <c r="R29" t="n">
-        <v>6706763.066953021</v>
+        <v>6706848.633460747</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4105,7 +4105,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96918182</v>
+        <v>96919412</v>
       </c>
       <c r="B30" t="n">
         <v>98520</v>
@@ -4140,15 +4140,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4156,10 +4160,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577854.1496546528</v>
+        <v>577873.0839795307</v>
       </c>
       <c r="R30" t="n">
-        <v>6706848.633460747</v>
+        <v>6706748.966252205</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4201,7 +4205,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4216,22 +4220,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96919412</v>
+        <v>96918986</v>
       </c>
       <c r="B31" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4240,42 +4244,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4283,10 +4274,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577873.0839795307</v>
+        <v>577836.4869757505</v>
       </c>
       <c r="R31" t="n">
-        <v>6706748.966252205</v>
+        <v>6706797.476779287</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4318,7 +4309,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4328,7 +4319,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4343,19 +4334,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96918986</v>
+        <v>96919902</v>
       </c>
       <c r="B32" t="n">
         <v>96334</v>
@@ -4388,7 +4379,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577836.4869757505</v>
+        <v>577791.9699620962</v>
       </c>
       <c r="R32" t="n">
-        <v>6706797.476779287</v>
+        <v>6706755.108541602</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4457,19 +4457,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96919902</v>
+        <v>96920282</v>
       </c>
       <c r="B33" t="n">
         <v>96334</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577791.9699620962</v>
+        <v>577832.1500053563</v>
       </c>
       <c r="R33" t="n">
-        <v>6706755.108541602</v>
+        <v>6706746.606215799</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96920282</v>
+        <v>96918394</v>
       </c>
       <c r="B34" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4604,35 +4604,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577832.1500053563</v>
+        <v>577884.7497534554</v>
       </c>
       <c r="R34" t="n">
-        <v>6706746.606215799</v>
+        <v>6706849.292275023</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4715,7 +4715,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96918394</v>
+        <v>96916777</v>
       </c>
       <c r="B35" t="n">
         <v>98520</v>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577884.7497534554</v>
+        <v>577893.5853840245</v>
       </c>
       <c r="R35" t="n">
-        <v>6706849.292275023</v>
+        <v>6706737.083026997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96916777</v>
+        <v>96920433</v>
       </c>
       <c r="B36" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4850,35 +4850,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577893.5853840245</v>
+        <v>577825.1340848273</v>
       </c>
       <c r="R36" t="n">
-        <v>6706737.083026997</v>
+        <v>6706751.385108472</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96920433</v>
+        <v>96916979</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4973,35 +4973,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577825.1340848273</v>
+        <v>577869.4537274459</v>
       </c>
       <c r="R37" t="n">
-        <v>6706751.385108472</v>
+        <v>6706734.098477424</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5084,10 +5084,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96916979</v>
+        <v>96919929</v>
       </c>
       <c r="B38" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5096,35 +5096,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577869.4537274459</v>
+        <v>577817.109854895</v>
       </c>
       <c r="R38" t="n">
-        <v>6706734.098477424</v>
+        <v>6706757.128283662</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5207,10 +5207,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96919929</v>
+        <v>96920479</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5219,30 +5219,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577817.109854895</v>
+        <v>577804.6601652051</v>
       </c>
       <c r="R39" t="n">
-        <v>6706757.128283662</v>
+        <v>6706784.9604748</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5330,7 +5330,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96920479</v>
+        <v>96917902</v>
       </c>
       <c r="B40" t="n">
         <v>98520</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5373,7 +5373,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5381,10 +5385,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577804.6601652051</v>
+        <v>577828.9129414055</v>
       </c>
       <c r="R40" t="n">
-        <v>6706784.9604748</v>
+        <v>6706759.354180517</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5416,7 +5420,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5426,7 +5430,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5441,22 +5445,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96917902</v>
+        <v>96918057</v>
       </c>
       <c r="B41" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5465,42 +5469,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5508,10 +5503,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577828.9129414055</v>
+        <v>577849.8179350846</v>
       </c>
       <c r="R41" t="n">
-        <v>6706759.354180517</v>
+        <v>6706774.593581008</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5543,7 +5538,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5553,7 +5548,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5568,22 +5563,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96918057</v>
+        <v>96918378</v>
       </c>
       <c r="B42" t="n">
-        <v>96334</v>
+        <v>89356</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5592,44 +5587,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577849.8179350846</v>
+        <v>577873.0839795307</v>
       </c>
       <c r="R42" t="n">
-        <v>6706774.593581008</v>
+        <v>6706748.966252205</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5661,7 +5653,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5671,7 +5663,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5680,28 +5672,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96918378</v>
+        <v>96918011</v>
       </c>
       <c r="B43" t="n">
-        <v>89356</v>
+        <v>96334</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5710,41 +5703,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577873.0839795307</v>
+        <v>577801.3232190479</v>
       </c>
       <c r="R43" t="n">
-        <v>6706748.966252205</v>
+        <v>6706825.31290188</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5776,7 +5777,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5786,7 +5787,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,29 +5796,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>96918011</v>
+        <v>96918063</v>
       </c>
       <c r="B44" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5826,37 +5826,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5865,10 +5856,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577801.3232190479</v>
+        <v>577849.8179350846</v>
       </c>
       <c r="R44" t="n">
-        <v>6706825.31290188</v>
+        <v>6706774.593581008</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5900,7 +5891,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5910,7 +5901,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5925,22 +5916,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>96916840</v>
+        <v>96918428</v>
       </c>
       <c r="B45" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5949,37 +5940,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5988,10 +5970,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577869.4749446097</v>
+        <v>577868.0210422443</v>
       </c>
       <c r="R45" t="n">
-        <v>6706733.112957588</v>
+        <v>6706754.773080517</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -6023,7 +6005,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6033,7 +6015,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6048,22 +6030,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96918063</v>
+        <v>96917323</v>
       </c>
       <c r="B46" t="n">
-        <v>98520</v>
+        <v>89356</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6076,36 +6058,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577849.8179350846</v>
+        <v>577870.1599858754</v>
       </c>
       <c r="R46" t="n">
-        <v>6706774.593581008</v>
+        <v>6706770.101646136</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6137,7 +6128,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6147,7 +6138,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6156,28 +6147,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>96918428</v>
+        <v>96933536</v>
       </c>
       <c r="B47" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6186,29 +6178,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6216,10 +6221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577868.0210422443</v>
+        <v>577878.0365272008</v>
       </c>
       <c r="R47" t="n">
-        <v>6706754.773080517</v>
+        <v>6706862.950927451</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6246,22 +6251,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6276,22 +6281,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96917323</v>
+        <v>96917443</v>
       </c>
       <c r="B48" t="n">
-        <v>89356</v>
+        <v>5113</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6304,34 +6309,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6339,10 +6338,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577870.1599858754</v>
+        <v>577870.8500600582</v>
       </c>
       <c r="R48" t="n">
-        <v>6706770.101646136</v>
+        <v>6706783.920011062</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6374,7 +6373,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6384,7 +6383,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6412,10 +6411,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96933536</v>
+        <v>96933693</v>
       </c>
       <c r="B49" t="n">
-        <v>98520</v>
+        <v>89356</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6428,39 +6427,25 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
@@ -6502,7 +6487,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6512,7 +6497,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6539,10 +6524,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96917443</v>
+        <v>96957011</v>
       </c>
       <c r="B50" t="n">
-        <v>5113</v>
+        <v>96334</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6551,43 +6536,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577870.8500600582</v>
+        <v>577847.176320438</v>
       </c>
       <c r="R50" t="n">
-        <v>6706783.920011062</v>
+        <v>6706851.441196652</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6614,22 +6596,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6638,29 +6620,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>John Lindström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>John Lindström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96933693</v>
+        <v>96958129</v>
       </c>
       <c r="B51" t="n">
-        <v>89356</v>
+        <v>5113</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6673,35 +6654,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577878.0365272008</v>
+        <v>577896.8016522306</v>
       </c>
       <c r="R51" t="n">
-        <v>6706862.950927451</v>
+        <v>6706771.168306431</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6728,22 +6715,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6758,22 +6745,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>John Lindström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>John Lindström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96957011</v>
+        <v>96957896</v>
       </c>
       <c r="B52" t="n">
-        <v>96334</v>
+        <v>90676</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6782,40 +6769,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577847.176320438</v>
+        <v>577896.6478577005</v>
       </c>
       <c r="R52" t="n">
-        <v>6706851.441196652</v>
+        <v>6706801.236857007</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6847,7 +6833,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6857,7 +6843,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6884,10 +6870,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>96958129</v>
+        <v>96957426</v>
       </c>
       <c r="B53" t="n">
-        <v>5113</v>
+        <v>96334</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6896,45 +6882,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577896.8016522306</v>
+        <v>577821.7592219531</v>
       </c>
       <c r="R53" t="n">
-        <v>6706771.168306431</v>
+        <v>6706770.53888068</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6966,7 +6947,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6976,7 +6957,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7003,10 +6984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>96957896</v>
+        <v>96957476</v>
       </c>
       <c r="B54" t="n">
-        <v>90676</v>
+        <v>96334</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7015,39 +6996,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577896.6478577005</v>
+        <v>577863.2295103844</v>
       </c>
       <c r="R54" t="n">
-        <v>6706801.236857007</v>
+        <v>6706816.785558879</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7079,7 +7061,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7089,7 +7071,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7116,7 +7098,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>96957426</v>
+        <v>96957247</v>
       </c>
       <c r="B55" t="n">
         <v>96334</v>
@@ -7158,10 +7140,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577821.7592219531</v>
+        <v>577781.6279686113</v>
       </c>
       <c r="R55" t="n">
-        <v>6706770.53888068</v>
+        <v>6706799.747466524</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7193,7 +7175,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7203,7 +7185,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7230,7 +7212,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>96957476</v>
+        <v>96957070</v>
       </c>
       <c r="B56" t="n">
         <v>96334</v>
@@ -7272,10 +7254,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577863.2295103844</v>
+        <v>577862.5818478146</v>
       </c>
       <c r="R56" t="n">
-        <v>6706816.785558879</v>
+        <v>6706800.99631863</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7307,7 +7289,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7317,7 +7299,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7344,10 +7326,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>96957247</v>
+        <v>96956655</v>
       </c>
       <c r="B57" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7356,25 +7338,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7386,10 +7368,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577781.6279686113</v>
+        <v>577896.5413729604</v>
       </c>
       <c r="R57" t="n">
-        <v>6706799.747466524</v>
+        <v>6706714.469167824</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7421,7 +7403,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7431,7 +7413,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7458,7 +7440,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96957070</v>
+        <v>96957105</v>
       </c>
       <c r="B58" t="n">
         <v>96334</v>
@@ -7500,10 +7482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577862.5818478146</v>
+        <v>577812.7644370208</v>
       </c>
       <c r="R58" t="n">
-        <v>6706800.99631863</v>
+        <v>6706798.445278856</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7535,7 +7517,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7545,7 +7527,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7572,7 +7554,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>96956655</v>
+        <v>97093447</v>
       </c>
       <c r="B59" t="n">
         <v>98520</v>
@@ -7606,18 +7588,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Söderåsen, östra sluttningen, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577896.5413729604</v>
+        <v>577868.5742447773</v>
       </c>
       <c r="R59" t="n">
-        <v>6706714.469167824</v>
+        <v>6706866.690959298</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7644,22 +7624,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2001-05-27</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2001-05-27</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7670,26 +7650,40 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Skog, öppen barrdominerad med lövinslag i fuktig svacka invid gråalbestånd</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 218395N</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>John Lindström</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>John Lindström</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Ove Lennström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>96957105</v>
+        <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>96334</v>
+        <v>99382</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7698,40 +7692,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221223</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Söderåsen, östra sluttningen, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577812.7644370208</v>
+        <v>577720.3893500492</v>
       </c>
       <c r="R60" t="n">
-        <v>6706798.445278856</v>
+        <v>6706892.095747682</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7758,22 +7750,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2001-07-09</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2001-07-09</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7784,26 +7776,40 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Berg, hällar, dock fläckvis täckt av ljung</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 218407N</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>John Lindström</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>John Lindström</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Ove Lennström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>97093447</v>
+        <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>98520</v>
+        <v>108194</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7816,21 +7822,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7840,10 +7846,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577868.5742447773</v>
+        <v>577880.737692422</v>
       </c>
       <c r="R61" t="n">
-        <v>6706866.690959298</v>
+        <v>6706852.163716358</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7870,7 +7876,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2001-05-27</t>
+          <t>2001-07-09</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -7880,7 +7886,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2001-05-27</t>
+          <t>2001-07-09</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -7899,12 +7905,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Skog, öppen barrdominerad med lövinslag i fuktig svacka invid gråalbestånd</t>
+          <t>skog, Tallskog, gles skog med inslag av gran</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 218395N</t>
+          <t>Gst Fyndnr 218422N</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7926,10 +7932,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>97093435</v>
+        <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>99382</v>
+        <v>108194</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7938,25 +7944,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221223</v>
+        <v>219711</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7966,10 +7972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577720.3893500492</v>
+        <v>577868.5742447773</v>
       </c>
       <c r="R62" t="n">
-        <v>6706892.095747682</v>
+        <v>6706866.690959298</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7996,7 +8002,7 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2001-07-09</t>
+          <t>2001-05-27</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -8006,7 +8012,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2001-07-09</t>
+          <t>2001-05-27</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8025,12 +8031,12 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Berg, hällar, dock fläckvis täckt av ljung</t>
+          <t>Skog, öppen barrdominerad med lövinslag i fuktig svacka invid gråalbestånd</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 218407N</t>
+          <t>Gst Fyndnr 218393N</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8052,10 +8058,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>97093420</v>
+        <v>96918329</v>
       </c>
       <c r="B63" t="n">
-        <v>108194</v>
+        <v>98520</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8068,34 +8074,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Söderåsen, östra sluttningen, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577880.737692422</v>
+        <v>577877.9559572283</v>
       </c>
       <c r="R63" t="n">
-        <v>6706852.163716358</v>
+        <v>6706752.029065706</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8122,22 +8130,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2001-07-09</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2001-07-09</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8148,40 +8156,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>skog, Tallskog, gles skog med inslag av gran</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 218422N</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ove Lennström</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>97093449</v>
+        <v>96918402</v>
       </c>
       <c r="B64" t="n">
-        <v>108194</v>
+        <v>98520</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8194,34 +8188,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Söderåsen, östra sluttningen, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577868.5742447773</v>
+        <v>577868.0210422443</v>
       </c>
       <c r="R64" t="n">
-        <v>6706866.690959298</v>
+        <v>6706754.773080517</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8248,22 +8244,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2001-05-27</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2001-05-27</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Källa?</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8274,82 +8275,74 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Skog, öppen barrdominerad med lövinslag i fuktig svacka invid gråalbestånd</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 218393N</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ove Lennström</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>96918329</v>
+        <v>96919135</v>
       </c>
       <c r="B65" t="n">
-        <v>98520</v>
+        <v>56395</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577877.9559572283</v>
+        <v>577873.0839795307</v>
       </c>
       <c r="R65" t="n">
-        <v>6706752.029065706</v>
+        <v>6706748.966252205</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8381,7 +8374,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8391,7 +8384,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8406,22 +8399,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>96918402</v>
+        <v>103252605</v>
       </c>
       <c r="B66" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8430,25 +8423,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8460,10 +8453,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577868.0210422443</v>
+        <v>577816.9932387691</v>
       </c>
       <c r="R66" t="n">
-        <v>6706754.773080517</v>
+        <v>6706762.548603038</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8490,27 +8483,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Källa?</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8525,70 +8513,72 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96919135</v>
+        <v>103252660</v>
       </c>
       <c r="B67" t="n">
-        <v>56395</v>
+        <v>90653</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577873.0839795307</v>
+        <v>577824.6394185176</v>
       </c>
       <c r="R67" t="n">
-        <v>6706748.966252205</v>
+        <v>6706705.526515356</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8615,22 +8605,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8645,22 +8635,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>103252605</v>
+        <v>103252668</v>
       </c>
       <c r="B68" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8669,25 +8659,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8699,10 +8689,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577816.9932387691</v>
+        <v>577833.7675539955</v>
       </c>
       <c r="R68" t="n">
-        <v>6706762.548603038</v>
+        <v>6706694.384100267</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8734,7 +8724,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8744,7 +8734,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8771,10 +8761,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>103252660</v>
+        <v>103252564</v>
       </c>
       <c r="B69" t="n">
-        <v>90653</v>
+        <v>96334</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8783,48 +8773,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577824.6394185176</v>
+        <v>577790.3212256778</v>
       </c>
       <c r="R69" t="n">
-        <v>6706705.526515356</v>
+        <v>6706808.808033765</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8856,7 +8838,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8866,7 +8848,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8893,10 +8875,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>103252668</v>
+        <v>103252872</v>
       </c>
       <c r="B70" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8905,25 +8887,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8935,10 +8917,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577833.7675539955</v>
+        <v>577874.6278544825</v>
       </c>
       <c r="R70" t="n">
-        <v>6706694.384100267</v>
+        <v>6706700.193525058</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8970,7 +8952,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8980,7 +8962,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8995,19 +8977,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>103252564</v>
+        <v>103253075</v>
       </c>
       <c r="B71" t="n">
         <v>96334</v>
@@ -9049,10 +9031,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577790.3212256778</v>
+        <v>577800.1877233427</v>
       </c>
       <c r="R71" t="n">
-        <v>6706808.808033765</v>
+        <v>6706832.190125667</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -9084,7 +9066,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9094,7 +9076,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9121,10 +9103,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>103252872</v>
+        <v>103252289</v>
       </c>
       <c r="B72" t="n">
-        <v>96334</v>
+        <v>88856</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9133,40 +9115,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577874.6278544825</v>
+        <v>577752.9295104028</v>
       </c>
       <c r="R72" t="n">
-        <v>6706700.193525058</v>
+        <v>6706848.42794419</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9198,7 +9181,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9208,7 +9191,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9217,25 +9200,26 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>103253075</v>
+        <v>103252537</v>
       </c>
       <c r="B73" t="n">
         <v>96334</v>
@@ -9268,8 +9252,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9277,10 +9274,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577800.1877233427</v>
+        <v>577752.9295104028</v>
       </c>
       <c r="R73" t="n">
-        <v>6706832.190125667</v>
+        <v>6706848.42794419</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9312,7 +9309,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9322,7 +9319,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9349,10 +9346,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>103252289</v>
+        <v>103269481</v>
       </c>
       <c r="B74" t="n">
-        <v>88856</v>
+        <v>92939</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9361,41 +9358,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2008</v>
+        <v>2779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577752.9295104028</v>
+        <v>577748.2716364675</v>
       </c>
       <c r="R74" t="n">
-        <v>6706848.42794419</v>
+        <v>6706766.493553843</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9422,22 +9418,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9446,29 +9442,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>103252537</v>
+        <v>103269435</v>
       </c>
       <c r="B75" t="n">
-        <v>96334</v>
+        <v>94121</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9477,53 +9472,40 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577752.9295104028</v>
+        <v>577748.2716364675</v>
       </c>
       <c r="R75" t="n">
-        <v>6706848.42794419</v>
+        <v>6706766.493553843</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9550,22 +9532,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9580,22 +9562,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>103269481</v>
+        <v>103269476</v>
       </c>
       <c r="B76" t="n">
-        <v>92939</v>
+        <v>93145</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9608,21 +9590,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Neckera complanata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Huebener</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9706,10 +9688,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>103269435</v>
+        <v>103269348</v>
       </c>
       <c r="B77" t="n">
-        <v>94121</v>
+        <v>93146</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9718,25 +9700,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>2666</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Neckera crispa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9820,10 +9802,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>103269476</v>
+        <v>103285679</v>
       </c>
       <c r="B78" t="n">
-        <v>93145</v>
+        <v>93146</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9836,39 +9818,49 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Neckera crispa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Söderåsen , Gstr</t>
+          <t>Söderåsen, skog N Stjärnsundsvägen, Gstr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577748.2716364675</v>
+        <v>577757.0074302087</v>
       </c>
       <c r="R78" t="n">
-        <v>6706766.493553843</v>
+        <v>6706773.583102306</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9910,34 +9902,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På klippvägg</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Barbro Risberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Barbro Risberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>103269348</v>
+        <v>103285627</v>
       </c>
       <c r="B79" t="n">
-        <v>93146</v>
+        <v>96337</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9950,36 +9948,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2666</v>
+        <v>223614</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Söderåsen , Gstr</t>
+          <t>Söderåsen, skog N Stjärnsundsvägen 2, Gstr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577748.2716364675</v>
+        <v>577822.0666837724</v>
       </c>
       <c r="R79" t="n">
-        <v>6706766.493553843</v>
+        <v>6706756.248961641</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10030,28 +10034,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Barbro Risberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Barbro Risberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>103285679</v>
+        <v>103474126</v>
       </c>
       <c r="B80" t="n">
-        <v>93146</v>
+        <v>78098</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10060,53 +10065,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2666</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Söderåsen, skog N Stjärnsundsvägen, Gstr</t>
+          <t>Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577757.0074302087</v>
+        <v>577635.1333217681</v>
       </c>
       <c r="R80" t="n">
-        <v>6706773.583102306</v>
+        <v>6706608.277504196</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10130,7 +10124,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
@@ -10140,7 +10134,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -10148,40 +10142,34 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På klippvägg</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Barbro Risberg</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Barbro Risberg</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>103285627</v>
+        <v>103475431</v>
       </c>
       <c r="B81" t="n">
-        <v>96337</v>
+        <v>96334</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10190,46 +10178,53 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>223614</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Söderåsen, skog N Stjärnsundsvägen 2, Gstr</t>
+          <t>Hofors Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577822.0666837724</v>
+        <v>577687.5251525929</v>
       </c>
       <c r="R81" t="n">
-        <v>6706756.248961641</v>
+        <v>6706743.989956657</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10256,22 +10251,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10280,29 +10275,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Barbro Risberg</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Barbro Risberg</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>103474126</v>
+        <v>103475753</v>
       </c>
       <c r="B82" t="n">
-        <v>78098</v>
+        <v>96334</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10311,39 +10305,53 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Söderåsen , Gstr</t>
+          <t>Hofors Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577635.1333217681</v>
+        <v>577714.1206296779</v>
       </c>
       <c r="R82" t="n">
-        <v>6706608.277504196</v>
+        <v>6706770.196460015</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10375,7 +10383,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10385,7 +10393,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10400,22 +10408,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>103475431</v>
+        <v>103477797</v>
       </c>
       <c r="B83" t="n">
-        <v>96334</v>
+        <v>79433</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10424,53 +10432,39 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hofors Söderåsen , Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577687.5251525929</v>
+        <v>577769.6968429537</v>
       </c>
       <c r="R83" t="n">
-        <v>6706743.989956657</v>
+        <v>6706642.720299357</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10502,7 +10496,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10512,7 +10506,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10527,19 +10521,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>103475753</v>
+        <v>103481526</v>
       </c>
       <c r="B84" t="n">
         <v>96334</v>
@@ -10572,35 +10566,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hofors Söderåsen , Gstr</t>
+          <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577714.1206296779</v>
+        <v>577735.0725693445</v>
       </c>
       <c r="R84" t="n">
-        <v>6706770.196460015</v>
+        <v>6706760.294054783</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10629,7 +10612,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10639,7 +10622,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10648,28 +10631,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>103477797</v>
+        <v>103481523</v>
       </c>
       <c r="B85" t="n">
-        <v>79433</v>
+        <v>95220</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10678,42 +10662,45 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1049</v>
+        <v>2609</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577769.6968429537</v>
+        <v>577735.0725693445</v>
       </c>
       <c r="R85" t="n">
-        <v>6706642.720299357</v>
+        <v>6706760.294054783</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10761,8 +10748,19 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>ravin i barrskog</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>sten, lodyta</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10779,7 +10777,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>103481526</v>
+        <v>103475625</v>
       </c>
       <c r="B86" t="n">
         <v>96334</v>
@@ -10812,24 +10810,35 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Söderåsen, Gstr</t>
+          <t>Hofors Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577735.0725693445</v>
+        <v>577681.1511504856</v>
       </c>
       <c r="R86" t="n">
-        <v>6706760.294054783</v>
+        <v>6706741.881113959</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10858,7 +10867,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10868,7 +10877,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10877,29 +10886,28 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>103481523</v>
+        <v>103475020</v>
       </c>
       <c r="B87" t="n">
-        <v>95220</v>
+        <v>78098</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10908,42 +10916,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2609</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Söderåsen, Gstr</t>
+          <t>Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>577735.0725693445</v>
+        <v>577628.5229100167</v>
       </c>
       <c r="R87" t="n">
-        <v>6706760.294054783</v>
+        <v>6706640.180729195</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10994,19 +10999,8 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>ravin i barrskog</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>sten, lodyta</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11023,10 +11017,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>103475625</v>
+        <v>103475062</v>
       </c>
       <c r="B88" t="n">
-        <v>96334</v>
+        <v>77506</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11035,53 +11029,39 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hofors Söderåsen , Gstr</t>
+          <t>Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>577681.1511504856</v>
+        <v>577640.2700358626</v>
       </c>
       <c r="R88" t="n">
-        <v>6706741.881113959</v>
+        <v>6706668.040721334</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -11113,7 +11093,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11123,7 +11103,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11138,19 +11118,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>103475020</v>
+        <v>103477437</v>
       </c>
       <c r="B89" t="n">
         <v>78098</v>
@@ -11187,17 +11167,17 @@
       <c r="K89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Söderåsen , Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>577628.5229100167</v>
+        <v>577782.0167655468</v>
       </c>
       <c r="R89" t="n">
-        <v>6706640.180729195</v>
+        <v>6706689.819905496</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11263,10 +11243,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>103475062</v>
+        <v>103474131</v>
       </c>
       <c r="B90" t="n">
-        <v>77506</v>
+        <v>77177</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11279,21 +11259,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11304,10 +11284,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>577640.2700358626</v>
+        <v>577635.1333217681</v>
       </c>
       <c r="R90" t="n">
-        <v>6706668.040721334</v>
+        <v>6706608.277504196</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -11376,10 +11356,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>103477437</v>
+        <v>103476698</v>
       </c>
       <c r="B91" t="n">
-        <v>78098</v>
+        <v>96334</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11388,39 +11368,48 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Hofors Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>577782.0167655468</v>
+        <v>577814.7256236642</v>
       </c>
       <c r="R91" t="n">
-        <v>6706689.819905496</v>
+        <v>6706707.285187398</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -11452,7 +11441,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11462,7 +11451,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11477,22 +11466,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>103474131</v>
+        <v>104631536</v>
       </c>
       <c r="B92" t="n">
-        <v>77177</v>
+        <v>79433</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11505,21 +11494,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11530,10 +11519,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>577635.1333217681</v>
+        <v>577553.378207235</v>
       </c>
       <c r="R92" t="n">
-        <v>6706608.277504196</v>
+        <v>6706598.142639205</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -11560,22 +11549,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11602,10 +11591,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>103476698</v>
+        <v>104631810</v>
       </c>
       <c r="B93" t="n">
-        <v>96334</v>
+        <v>78098</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11614,48 +11603,39 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hofors Söderåsen , Gstr</t>
+          <t>Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>577814.7256236642</v>
+        <v>577552.3940203935</v>
       </c>
       <c r="R93" t="n">
-        <v>6706707.285187398</v>
+        <v>6706574.950250505</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11682,22 +11662,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11712,22 +11692,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>104631536</v>
+        <v>104631538</v>
       </c>
       <c r="B94" t="n">
-        <v>79433</v>
+        <v>77177</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11740,21 +11720,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11837,10 +11817,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>104631810</v>
+        <v>103252667</v>
       </c>
       <c r="B95" t="n">
-        <v>78098</v>
+        <v>97165</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11849,39 +11829,40 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Söderåsen , Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>577552.3940203935</v>
+        <v>577820</v>
       </c>
       <c r="R95" t="n">
-        <v>6706574.950250505</v>
+        <v>6706709</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11908,22 +11889,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11938,22 +11919,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>104631538</v>
+        <v>114715064</v>
       </c>
       <c r="B96" t="n">
-        <v>77177</v>
+        <v>5165</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11962,42 +11943,50 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Söderåsen , Gstr</t>
+          <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>577553.378207235</v>
+        <v>577564</v>
       </c>
       <c r="R96" t="n">
-        <v>6706598.142639205</v>
+        <v>6706581</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12021,22 +12010,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12045,28 +12024,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Philipp Weiss, fanny westling</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>103252667</v>
+        <v>114715045</v>
       </c>
       <c r="B97" t="n">
-        <v>97165</v>
+        <v>79099</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12075,43 +12055,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>577820</v>
+        <v>577639</v>
       </c>
       <c r="R97" t="n">
-        <v>6706709</v>
+        <v>6706612</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12135,22 +12113,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12165,22 +12133,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss, fanny westling</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>114715064</v>
+        <v>114715042</v>
       </c>
       <c r="B98" t="n">
-        <v>5165</v>
+        <v>90297</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12193,43 +12161,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>577564</v>
+        <v>577614</v>
       </c>
       <c r="R98" t="n">
-        <v>6706581</v>
+        <v>6706604</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -12270,7 +12229,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -12289,7 +12247,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>114715045</v>
+        <v>114715044</v>
       </c>
       <c r="B99" t="n">
         <v>79099</v>
@@ -12329,10 +12287,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577639</v>
+        <v>577545</v>
       </c>
       <c r="R99" t="n">
-        <v>6706612</v>
+        <v>6706576</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -12391,10 +12349,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>114715042</v>
+        <v>114715047</v>
       </c>
       <c r="B100" t="n">
-        <v>90297</v>
+        <v>90332</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12403,25 +12361,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12431,10 +12389,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577614</v>
+        <v>577488</v>
       </c>
       <c r="R100" t="n">
-        <v>6706604</v>
+        <v>6706545</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -12493,10 +12451,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>114715044</v>
+        <v>114715046</v>
       </c>
       <c r="B101" t="n">
-        <v>79099</v>
+        <v>90332</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12509,21 +12467,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12533,10 +12491,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>577545</v>
+        <v>577701</v>
       </c>
       <c r="R101" t="n">
-        <v>6706576</v>
+        <v>6706738</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -12595,10 +12553,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>114715047</v>
+        <v>114715058</v>
       </c>
       <c r="B102" t="n">
-        <v>90332</v>
+        <v>78157</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12611,21 +12569,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12635,10 +12593,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>577488</v>
+        <v>577639</v>
       </c>
       <c r="R102" t="n">
-        <v>6706545</v>
+        <v>6706601</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -12697,10 +12655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>114715046</v>
+        <v>114715040</v>
       </c>
       <c r="B103" t="n">
-        <v>90332</v>
+        <v>5185</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12709,38 +12667,47 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>577701</v>
+        <v>577825</v>
       </c>
       <c r="R103" t="n">
-        <v>6706738</v>
+        <v>6706716</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -12781,6 +12748,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12799,10 +12767,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>114715058</v>
+        <v>114715061</v>
       </c>
       <c r="B104" t="n">
-        <v>78157</v>
+        <v>5165</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12811,38 +12779,47 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>577639</v>
+        <v>577632</v>
       </c>
       <c r="R104" t="n">
-        <v>6706601</v>
+        <v>6706672</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -12883,6 +12860,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12901,10 +12879,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>114715040</v>
+        <v>114715059</v>
       </c>
       <c r="B105" t="n">
-        <v>5185</v>
+        <v>79593</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12917,43 +12895,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>105930</v>
+        <v>6463</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>577825</v>
+        <v>577577</v>
       </c>
       <c r="R105" t="n">
-        <v>6706716</v>
+        <v>6706592</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -12994,7 +12963,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13013,7 +12981,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>114715061</v>
+        <v>114715062</v>
       </c>
       <c r="B106" t="n">
         <v>5165</v>
@@ -13062,10 +13030,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>577632</v>
+        <v>577442</v>
       </c>
       <c r="R106" t="n">
-        <v>6706672</v>
+        <v>6706535</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -13125,10 +13093,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>114715059</v>
+        <v>114715048</v>
       </c>
       <c r="B107" t="n">
-        <v>79593</v>
+        <v>90332</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13137,25 +13105,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13165,10 +13133,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>577577</v>
+        <v>577648</v>
       </c>
       <c r="R107" t="n">
-        <v>6706592</v>
+        <v>6706596</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -13227,7 +13195,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>114715062</v>
+        <v>114715063</v>
       </c>
       <c r="B108" t="n">
         <v>5165</v>
@@ -13276,10 +13244,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>577442</v>
+        <v>577477</v>
       </c>
       <c r="R108" t="n">
-        <v>6706535</v>
+        <v>6706556</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -13339,10 +13307,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>114715048</v>
+        <v>114715060</v>
       </c>
       <c r="B109" t="n">
-        <v>90332</v>
+        <v>5165</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13351,38 +13319,47 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>577648</v>
+        <v>577818</v>
       </c>
       <c r="R109" t="n">
-        <v>6706596</v>
+        <v>6706713</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -13423,6 +13400,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13438,230 +13416,6 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>114715063</v>
-      </c>
-      <c r="B110" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Söderåsen, Gstr</t>
-        </is>
-      </c>
-      <c r="Q110" t="n">
-        <v>577477</v>
-      </c>
-      <c r="R110" t="n">
-        <v>6706556</v>
-      </c>
-      <c r="S110" t="n">
-        <v>15</v>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AD110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF110" t="inlineStr"/>
-      <c r="AG110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT110" t="inlineStr"/>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>Philipp Weiss, fanny westling</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>114715060</v>
-      </c>
-      <c r="B111" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Söderåsen, Gstr</t>
-        </is>
-      </c>
-      <c r="Q111" t="n">
-        <v>577818</v>
-      </c>
-      <c r="R111" t="n">
-        <v>6706713</v>
-      </c>
-      <c r="S111" t="n">
-        <v>15</v>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AD111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF111" t="inlineStr"/>
-      <c r="AG111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT111" t="inlineStr"/>
-      <c r="AW111" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>Philipp Weiss, fanny westling</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -12658,12 +12658,7 @@
         <v>114715040</v>
       </c>
       <c r="B103" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5196</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -12658,7 +12658,7 @@
         <v>114715040</v>
       </c>
       <c r="B103" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13412,6 +13412,200 @@
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127701732</v>
+      </c>
+      <c r="B110" t="n">
+        <v>95779</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>577790</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6706745</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127701697</v>
+      </c>
+      <c r="B111" t="n">
+        <v>95781</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>577790</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6706745</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95781</v>
+        <v>95783</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95783</v>
+        <v>95789</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95789</v>
+        <v>95792</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95792</v>
+        <v>95800</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95800</v>
+        <v>95801</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95801</v>
+        <v>95802</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95800</v>
+        <v>95801</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95802</v>
+        <v>95803</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95801</v>
+        <v>95809</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95803</v>
+        <v>95811</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -13417,7 +13417,7 @@
         <v>127701732</v>
       </c>
       <c r="B110" t="n">
-        <v>95809</v>
+        <v>95821</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>127701697</v>
       </c>
       <c r="B111" t="n">
-        <v>95811</v>
+        <v>95823</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,12 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>97034</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,10 +2651,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577706.8665424174</v>
+        <v>577707</v>
       </c>
       <c r="R18" t="n">
-        <v>6706878.002115291</v>
+        <v>6706878</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2689,19 +2684,9 @@
           <t>2006-06-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2006-06-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2745,12 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,10 +2762,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577706.8665424174</v>
+        <v>577707</v>
       </c>
       <c r="R19" t="n">
-        <v>6706878.002115291</v>
+        <v>6706878</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2815,19 +2795,9 @@
           <t>2006-06-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2006-06-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -7557,12 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7594,10 +7559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577868.5742447773</v>
+        <v>577869</v>
       </c>
       <c r="R59" t="n">
-        <v>6706866.690959298</v>
+        <v>6706867</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7627,19 +7592,9 @@
           <t>2001-05-27</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2001-05-27</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7683,12 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101649</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7720,10 +7670,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577720.3893500492</v>
+        <v>577720</v>
       </c>
       <c r="R60" t="n">
-        <v>6706892.095747682</v>
+        <v>6706892</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7753,19 +7703,9 @@
           <t>2001-07-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2001-07-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7809,12 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110682</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7846,10 +7781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577880.737692422</v>
+        <v>577881</v>
       </c>
       <c r="R61" t="n">
-        <v>6706852.163716358</v>
+        <v>6706852</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7879,19 +7814,9 @@
           <t>2001-07-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2001-07-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7935,12 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110682</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7972,10 +7892,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577868.5742447773</v>
+        <v>577869</v>
       </c>
       <c r="R62" t="n">
-        <v>6706866.690959298</v>
+        <v>6706867</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -8005,19 +7925,9 @@
           <t>2001-05-27</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2001-05-27</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101649</v>
+        <v>101657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101649</v>
+        <v>101657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110682</v>
+        <v>110691</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110682</v>
+        <v>110691</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99320</v>
+        <v>99323</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101657</v>
+        <v>101662</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101657</v>
+        <v>101662</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110691</v>
+        <v>110704</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110691</v>
+        <v>110704</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99329</v>
+        <v>99356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99356</v>
+        <v>99362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99362</v>
+        <v>99369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13516,6 +13516,113 @@
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128917551</v>
+      </c>
+      <c r="B112" t="n">
+        <v>97316</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Östra Söderåsgruvorna, Östra Söderåsgruvorna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>577771</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6706833</v>
+      </c>
+      <c r="S112" t="n">
+        <v>9</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99369</v>
+        <v>99373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>128917551</v>
       </c>
       <c r="B112" t="n">
-        <v>97316</v>
+        <v>97320</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 37176-2022 artfynd.xlsx
+++ b/artfynd/A 37176-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2619,7 +2619,7 @@
         <v>91281512</v>
       </c>
       <c r="B18" t="n">
-        <v>99373</v>
+        <v>99380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>91281511</v>
       </c>
       <c r="B19" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>97093447</v>
       </c>
       <c r="B59" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>97093435</v>
       </c>
       <c r="B60" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>97093420</v>
       </c>
       <c r="B61" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>97093449</v>
       </c>
       <c r="B62" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>128917551</v>
       </c>
       <c r="B112" t="n">
-        <v>97320</v>
+        <v>97327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13622,6 +13622,113 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128915848</v>
+      </c>
+      <c r="B113" t="n">
+        <v>100831</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>577739</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6706776</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
